--- a/r4-core-80-include-testscripts/ValueSet-at-funktionscode-vs.xlsx
+++ b/r4-core-80-include-testscripts/ValueSet-at-funktionscode-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T08:45:14+00:00</t>
+    <t>2026-10-15T11:23:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-80-include-testscripts/ValueSet-at-funktionscode-vs.xlsx
+++ b/r4-core-80-include-testscripts/ValueSet-at-funktionscode-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:23:47+00:00</t>
+    <t>2026-10-16T06:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-80-include-testscripts/ValueSet-at-funktionscode-vs.xlsx
+++ b/r4-core-80-include-testscripts/ValueSet-at-funktionscode-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T06:17:07+00:00</t>
+    <t>2026-10-16T08:44:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
